--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-resultats-examens-biologie-medicale.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-resultats-examens-biologie-medicale.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="164">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,16 +455,6 @@
   </si>
   <si>
     <t>Code dont dérive le code de section</t>
-  </si>
-  <si>
-    <t>fr-lm-resultats-examens-biologie-medicale.choice[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-sujet-non-humain
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-sujet-non-humain</t>
-  </si>
-  <si>
-    <t>Sujet non humain ou Patient avec sujet non humain</t>
   </si>
   <si>
     <t>fr-lm-resultats-examens-biologie-medicale.laboratoireExecutant</t>
@@ -836,7 +826,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ28"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.640625" customWidth="true" bestFit="true"/>
@@ -2902,7 +2892,7 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2977,7 +2967,7 @@
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
@@ -3583,106 +3573,6 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q28" s="2"/>
-      <c r="R28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
         <v>73</v>
       </c>
     </row>
